--- a/artfynd/A 15950-2026 artfynd.xlsx
+++ b/artfynd/A 15950-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>114694292</v>
       </c>
       <c r="B2" t="n">
-        <v>57952</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">

--- a/artfynd/A 15950-2026 artfynd.xlsx
+++ b/artfynd/A 15950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114694292</v>
+        <v>134751664</v>
       </c>
       <c r="B2" t="n">
-        <v>58656</v>
+        <v>58596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103056</v>
+        <v>103041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>runt Kaunisvaara, Nb</t>
+          <t>Kaunisvaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>861874</v>
+        <v>861857</v>
       </c>
       <c r="R2" t="n">
-        <v>7498336</v>
+        <v>7498389</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 ex sjungande</t>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,11 +776,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jörgen Olsson</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -784,10 +784,126 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114694292</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58656</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>runt Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>861874</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7498336</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-05-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-05-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 ex sjungande</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>Jörgen Olsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 15950-2026 artfynd.xlsx
+++ b/artfynd/A 15950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134751664</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114694292</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>